--- a/docs/tech/JMocha_시스템_사이징_사용자수별.xlsx
+++ b/docs/tech/JMocha_시스템_사이징_사용자수별.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\kaoni\jmocha\sizing\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Projects\kaoni\jmocha\ezFlow4Java\docs\tech\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="68">
   <si>
     <t>Software</t>
   </si>
@@ -55,23 +55,6 @@
     <t>2(단중화)
 3(이중화)</t>
     <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tomcat, GlusterFS(이중화 시)
-JMocha Gateway Server, JMocha Mail Server, MariaDB</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tomcat, GlusterFS(이중화 시)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>JMocha Gateway Server, JMocha Mail Server, MariaDB</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>JMocha Gateway Server, JMocha Mail Server, MariaDB</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -146,10 +129,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>• garbd는 MariaDB Cluster의 노드수를 홀수로 만들기 위해 사용하는 가상노드임</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">• HDD는 SAS 10,000rpm 이상 필요
 </t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -172,13 +151,112 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>1 x 6core
-2.4GHz</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>24GB</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>10,000명</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>서버당 Storage</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2(단중화)
+3(이중화)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>구분</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>항목</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>보정수치</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>산정값</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>내역</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>전체사용자</t>
+  </si>
+  <si>
+    <t>전체사용자수</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1인당 메일 할당량 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1인당 메일 평균 제공용량</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>대용량 첨부파일 (1인당 사용량)</t>
+  </si>
+  <si>
+    <t>대용량 첨부파일 14일간 보존 기준</t>
+  </si>
+  <si>
+    <t>메일 용량 / Mbytes</t>
+  </si>
+  <si>
+    <t>로컬 시스템 용량 
+(Tbytes)</t>
+  </si>
+  <si>
+    <t>메일 용량 (Tbytes)</t>
+  </si>
+  <si>
+    <t>메일 용량</t>
+  </si>
+  <si>
+    <t>DB 용량 (Tbytes)</t>
+  </si>
+  <si>
+    <t>DB 용량</t>
+  </si>
+  <si>
+    <t>Storage 여유율</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Disk 사용률 90%이하 유지 권장</t>
+  </si>
+  <si>
+    <t>총 Storage 사용량</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이중화시 서버마다 다른 Data가 저장되는 용량</t>
+  </si>
+  <si>
+    <t>로컬 리스템 용량</t>
+  </si>
+  <si>
+    <t>이중화시 서버간 동일 Data가 저장되는 File Data 용량
+(GlusterFS의 경우엔 복제 방식이므로 서버당 용량이 필요하며 NAS 혹은 네트워크 파일 시스템을 사용할 경우엔 단일 용량만 필요)</t>
+  </si>
+  <si>
+    <t>이중화시 서버간 동일 Data가 저장되는 DB Data 용량 
+(MariaDB의 경우엔 복제 방식이므로 서버당 용량이 필요하며  Oracle의 경우엔 Shared Disk 방식이므로 단일 용량만 필요)</t>
+  </si>
+  <si>
+    <t>아래 계산표 참조</t>
+  </si>
+  <si>
+    <t>• garbd는 MariaDB Cluster의 노드수를 3개로 만들기 위해 사용하는 가상노드임</t>
+  </si>
+  <si>
+    <t>Tomcat, GlusterFS(이중화 시)
+JMocha Mail Server, MariaDB</t>
   </si>
   <si>
     <r>
@@ -189,211 +267,21 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>garbd(이중화 시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Tomcat, GlusterFS(이중화 시), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>garbd(이중화 시)</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>10,000명</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>서버당 Storage</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1 x 12core
-2.4GHz</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>48GB</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>2(단중화)
-3(이중화)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve"> - 사용자당 메일박스용량 x 1.2 x 사용자수
-   예) 사용자당 1GB일 경우 1GB x 1.2 x 1,000 = 1.2TB
- - 사용자당 대용량 첨부 파일저장용량 x 사용자수
-   예) 보관기간 14일 동안 사용자당 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>100MB 사용할 경우 100MB x 1,000 = 100GB</t>
+      <t xml:space="preserve">garbd(이중화 </t>
     </r>
     <r>
       <rPr>
         <sz val="8"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
- - 메일 큐(1인당 100MB) 및 로그 저장용(1인당 200MB) x 사용자수
-   예) (0.1 + 0.2) x 1,000 = 300GB</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> - 사용자당 메일박스용량 x 1.2 x 사용자수
-   예) 사용자당 1GB일 경우 1GB x 1.2 x 3,000 = 3.6TB
- - 메일 큐(1인당 100MB) 및 로그 저장용(1인당 100MB) x 사용자수
-   예) (0.1 + 0.1) x 3,000 = 600GB</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve"> - 사용자당 대용량 첨부 파일저장용량 x 사용자수
-   예) 보관기간 14일 동안 사용자당 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>100MB 사용할 경우 100MB x 5,000 = 500GB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
- - 로그 저장용(1인당 100MB) x 사용자수
-   예) 0.1 x 5,000 = 500GB</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve"> - 사용자당 대용량 첨부 파일저장용량 x 사용자수
-   예) 보관기간 14일 동안 사용자당 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>100MB 사용할 경우 100MB x 3,000 = 300GB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
- - 로그 저장용(1인당 100MB) x 사용자수
-   예) 0.1 x 3,000 = 300GB</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> - 사용자당 메일박스용량 x 1.2 x 사용자수
-   예) 사용자당 1GB일 경우 1GB x 1.2 x 10,000 = 12TB
- - 메일 큐(1인당 100MB) 및 로그 저장용(1인당 100MB) x 사용자수 / 서버대수
-   예) (0.1 + 0.1) x 10,000 / 2 = 1TB</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> - 사용자당 메일박스용량 x 1.2 x 사용자수
-   예) 사용자당 1GB일 경우 1GB x 1.2 x 5,000 = 6TB
- - 메일 큐(1인당 100MB) 및 로그 저장용(1인당 100MB) x 사용자수 / 서버대수
-   예) (0.1 + 0.1) x 5,000 / 2 = 500GB</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve"> - 사용자당 대용량 첨부 파일저장용량 x 사용자수 / 서버대수
-   예) 보관기간 14일 동안 사용자당 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>100MB 사용할 경우 100MB x 10,000 / 2 = 500GB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
- - 로그 저장용(1인당 100MB) x 사용자수 / 서버대수
-   예) 0.1 x 10,000 / 2 = 500GB</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
+      <t>시)</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t>2</t>
     </r>
     <r>
@@ -411,7 +299,7 @@
     <r>
       <rPr>
         <sz val="8"/>
-        <color rgb="FFFF0000"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -430,15 +318,69 @@
       <t>(이중화)</t>
     </r>
   </si>
+  <si>
+    <t>MariaDB</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Tomcat, GlusterFS(이중화 시), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>garbd(이중화 시)
+JMocha Mail Server</t>
+    </r>
+  </si>
+  <si>
+    <t>Tomcat, GlusterFS(이중화 시)
+JMocha Mail Server</t>
+  </si>
+  <si>
+    <t>1 x 4core
+2.4GHz</t>
+  </si>
+  <si>
+    <t>1 x 8core
+2.4GHz</t>
+  </si>
+  <si>
+    <t>1 x 16core
+2.4GHz</t>
+  </si>
+  <si>
+    <t>36GB</t>
+  </si>
+  <si>
+    <t>12GB</t>
+  </si>
+  <si>
+    <t>24GB</t>
+  </si>
+  <si>
+    <t>72GB</t>
+  </si>
+  <si>
+    <t>메일 큐(1인당 100MB)및 LOG 사용량(1인당 200MB) (이중화시 서버간 공유되지 않음)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="1">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="#,##0\ &quot;MB&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0000\ &quot;TB&quot;"/>
+    <numFmt numFmtId="168" formatCode="#,##0.00\ &quot;TB&quot;"/>
+    <numFmt numFmtId="169" formatCode="#,##0.00\ &quot;%&quot;"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -528,20 +470,47 @@
     </font>
     <font>
       <sz val="8"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -560,8 +529,32 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -701,13 +694,55 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="41" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -750,6 +785,27 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -762,29 +818,108 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="14" fillId="6" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="14" fillId="6" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="13" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="13" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="13" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="13" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="15" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="15" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="14" fillId="7" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="14" fillId="7" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1063,7 +1198,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -1076,56 +1211,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="16"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
+      <c r="A2" s="23"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
     </row>
     <row r="3" spans="1:7" ht="30.75" customHeight="1">
-      <c r="A3" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
+      <c r="A3" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
       <c r="G3" s="5"/>
     </row>
     <row r="4" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
     </row>
     <row r="5" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A5" s="18" t="s">
-        <v>13</v>
+      <c r="A5" s="20" t="s">
+        <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>1</v>
@@ -1134,64 +1269,64 @@
         <v>2</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="74.25" customHeight="1" thickBot="1">
-      <c r="A6" s="19"/>
+      <c r="A6" s="16"/>
       <c r="B6" s="8" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="46.5" customHeight="1">
-      <c r="A7" s="20"/>
+      <c r="A7" s="17"/>
       <c r="B7" s="11" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="C7" s="6">
         <v>1</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15.75" thickBot="1"/>
     <row r="9" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A9" s="18" t="s">
-        <v>14</v>
+      <c r="A9" s="20" t="s">
+        <v>10</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>1</v>
@@ -1200,62 +1335,62 @@
         <v>2</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="57" customHeight="1" thickBot="1">
-      <c r="A10" s="19"/>
-      <c r="B10" s="3" t="s">
-        <v>33</v>
+      <c r="A10" s="16"/>
+      <c r="B10" s="8" t="s">
+        <v>58</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G10" s="21" t="s">
-        <v>25</v>
+        <v>52</v>
+      </c>
+      <c r="G10" s="18" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="56.25" customHeight="1">
-      <c r="A11" s="20"/>
+      <c r="A11" s="17"/>
       <c r="B11" s="3" t="s">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="G11" s="22"/>
+        <v>52</v>
+      </c>
+      <c r="G11" s="19"/>
     </row>
     <row r="12" spans="1:7" ht="15.75" thickBot="1"/>
     <row r="13" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A13" s="18" t="s">
-        <v>15</v>
+      <c r="A13" s="20" t="s">
+        <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>1</v>
@@ -1264,62 +1399,62 @@
         <v>2</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="57" customHeight="1" thickBot="1">
-      <c r="A14" s="19"/>
-      <c r="B14" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="24" t="s">
-        <v>46</v>
+      <c r="A14" s="16"/>
+      <c r="B14" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>56</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="G14" s="21" t="s">
-        <v>26</v>
+        <v>52</v>
+      </c>
+      <c r="G14" s="18" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="56.25" customHeight="1">
-      <c r="A15" s="20"/>
+      <c r="A15" s="17"/>
       <c r="B15" s="3" t="s">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="G15" s="22"/>
+        <v>52</v>
+      </c>
+      <c r="G15" s="19"/>
     </row>
     <row r="16" spans="1:7" ht="15.75" thickBot="1"/>
     <row r="17" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A17" s="23" t="s">
-        <v>34</v>
+      <c r="A17" s="15" t="s">
+        <v>25</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>1</v>
@@ -1328,64 +1463,266 @@
         <v>2</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="G17" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="57" customHeight="1" thickBot="1">
+      <c r="A18" s="16"/>
+      <c r="B18" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="G18" s="18" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="57" customHeight="1" thickBot="1">
-      <c r="A18" s="19"/>
-      <c r="B18" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="G18" s="21" t="s">
-        <v>27</v>
-      </c>
-    </row>
     <row r="19" spans="1:7" ht="56.25" customHeight="1">
-      <c r="A19" s="20"/>
+      <c r="A19" s="17"/>
       <c r="B19" s="3" t="s">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D19" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="G19" s="19"/>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="B21" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="E21" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="F21" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="G21" s="27"/>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="B22" s="28">
+        <v>1</v>
+      </c>
+      <c r="C22" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="D22" s="29">
+        <v>1000</v>
+      </c>
+      <c r="E22" s="29"/>
+      <c r="F22" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="G22" s="31"/>
+    </row>
+    <row r="23" spans="1:7" ht="25.5">
+      <c r="B23" s="28">
+        <v>2</v>
+      </c>
+      <c r="C23" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="D23" s="32">
+        <v>1000</v>
+      </c>
+      <c r="E23" s="33"/>
+      <c r="F23" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="E19" s="13" t="s">
+      <c r="G23" s="31"/>
+    </row>
+    <row r="24" spans="1:7" ht="51">
+      <c r="B24" s="28">
+        <v>3</v>
+      </c>
+      <c r="C24" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="D24" s="32">
+        <v>100</v>
+      </c>
+      <c r="E24" s="43"/>
+      <c r="F24" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="G24" s="36"/>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="B25" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="C25" s="38"/>
+      <c r="D25" s="39">
+        <f>D22*D23 + D22*D24</f>
+        <v>1100000</v>
+      </c>
+      <c r="E25" s="40"/>
+      <c r="F25" s="41"/>
+      <c r="G25" s="42"/>
+    </row>
+    <row r="26" spans="1:7" ht="38.25">
+      <c r="B26" s="28">
+        <v>1</v>
+      </c>
+      <c r="C26" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="D26" s="44">
+        <f>0.0001*D22 + 0.0002*D22</f>
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="E26" s="45"/>
+      <c r="F26" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="G26" s="31"/>
+    </row>
+    <row r="27" spans="1:7" ht="25.5">
+      <c r="B27" s="28">
+        <v>3</v>
+      </c>
+      <c r="C27" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="D27" s="46">
+        <f>D25/1000000</f>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E27" s="47"/>
+      <c r="F27" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="G27" s="31"/>
+    </row>
+    <row r="28" spans="1:7" ht="25.5">
+      <c r="B28" s="28">
+        <v>4</v>
+      </c>
+      <c r="C28" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="G19" s="22"/>
+      <c r="D28" s="46">
+        <f>(D22*D23*0.2)/1000000</f>
+        <v>0.2</v>
+      </c>
+      <c r="E28" s="47"/>
+      <c r="F28" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="G28" s="31"/>
+    </row>
+    <row r="29" spans="1:7" ht="25.5">
+      <c r="B29" s="28">
+        <v>5</v>
+      </c>
+      <c r="C29" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="D29" s="48">
+        <v>10</v>
+      </c>
+      <c r="E29" s="49">
+        <f>SUM(D26:E28)/(1 - D29/100)</f>
+        <v>1.7777777777777779</v>
+      </c>
+      <c r="F29" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="G29" s="31"/>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="B30" s="50" t="s">
+        <v>47</v>
+      </c>
+      <c r="C30" s="51"/>
+      <c r="D30" s="52">
+        <f>E29</f>
+        <v>1.7777777777777779</v>
+      </c>
+      <c r="E30" s="53"/>
+      <c r="F30" s="54"/>
+      <c r="G30" s="55"/>
+    </row>
+    <row r="32" spans="1:7" ht="30">
+      <c r="B32" s="56" t="s">
+        <v>48</v>
+      </c>
+      <c r="C32" s="57" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" ht="90">
+      <c r="B33" s="56" t="s">
+        <v>50</v>
+      </c>
+      <c r="C33" s="57" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" ht="90">
+      <c r="B34" s="56" t="s">
+        <v>51</v>
+      </c>
+      <c r="C34" s="57" t="s">
+        <v>44</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="26">
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A1:G2"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="G10:G11"/>
     <mergeCell ref="A17:A19"/>
     <mergeCell ref="G18:G19"/>
     <mergeCell ref="A13:A15"/>
     <mergeCell ref="G14:G15"/>
     <mergeCell ref="A5:A7"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A1:G2"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="G10:G11"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/tech/JMocha_시스템_사이징_사용자수별.xlsx
+++ b/docs/tech/JMocha_시스템_사이징_사용자수별.xlsx
@@ -322,8 +322,35 @@
     <t>MariaDB</t>
   </si>
   <si>
+    <t>1 x 4core
+2.4GHz</t>
+  </si>
+  <si>
+    <t>1 x 8core
+2.4GHz</t>
+  </si>
+  <si>
+    <t>1 x 16core
+2.4GHz</t>
+  </si>
+  <si>
+    <t>36GB</t>
+  </si>
+  <si>
+    <t>12GB</t>
+  </si>
+  <si>
+    <t>24GB</t>
+  </si>
+  <si>
+    <t>72GB</t>
+  </si>
+  <si>
+    <t>메일 큐(1인당 100MB)및 LOG 사용량(1인당 200MB) (이중화시 서버간 공유되지 않음)</t>
+  </si>
+  <si>
     <r>
-      <t xml:space="preserve">Tomcat, GlusterFS(이중화 시), </t>
+      <t>Tomcat,</t>
     </r>
     <r>
       <rPr>
@@ -333,40 +360,13 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>garbd(이중화 시)
+      <t xml:space="preserve">
 JMocha Mail Server</t>
     </r>
   </si>
   <si>
-    <t>Tomcat, GlusterFS(이중화 시)
+    <t>Tomcat,
 JMocha Mail Server</t>
-  </si>
-  <si>
-    <t>1 x 4core
-2.4GHz</t>
-  </si>
-  <si>
-    <t>1 x 8core
-2.4GHz</t>
-  </si>
-  <si>
-    <t>1 x 16core
-2.4GHz</t>
-  </si>
-  <si>
-    <t>36GB</t>
-  </si>
-  <si>
-    <t>12GB</t>
-  </si>
-  <si>
-    <t>24GB</t>
-  </si>
-  <si>
-    <t>72GB</t>
-  </si>
-  <si>
-    <t>메일 큐(1인당 100MB)및 LOG 사용량(1인당 200MB) (이중화시 서버간 공유되지 않음)</t>
   </si>
 </sst>
 </file>
@@ -375,10 +375,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="#,##0\ &quot;MB&quot;"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0000\ &quot;TB&quot;"/>
-    <numFmt numFmtId="168" formatCode="#,##0.00\ &quot;TB&quot;"/>
-    <numFmt numFmtId="169" formatCode="#,##0.00\ &quot;%&quot;"/>
+    <numFmt numFmtId="164" formatCode="#,##0\ &quot;MB&quot;"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0000\ &quot;TB&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00\ &quot;TB&quot;"/>
+    <numFmt numFmtId="167" formatCode="#,##0.00\ &quot;%&quot;"/>
   </numFmts>
   <fonts count="16">
     <font>
@@ -788,7 +788,118 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="13" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="14" fillId="7" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="14" fillId="7" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="14" fillId="6" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="14" fillId="6" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -803,118 +914,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="14" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="14" fillId="6" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="14" fillId="6" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="14" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="13" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="13" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="13" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="13" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="15" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="15" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="14" fillId="7" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="14" fillId="7" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1211,49 +1211,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="23"/>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
+      <c r="A2" s="50"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
     </row>
     <row r="3" spans="1:7" ht="30.75" customHeight="1">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
       <c r="G3" s="5"/>
     </row>
     <row r="4" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="24"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
     </row>
     <row r="5" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="52" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -1276,7 +1276,7 @@
       </c>
     </row>
     <row r="6" spans="1:7" ht="74.25" customHeight="1" thickBot="1">
-      <c r="A6" s="16"/>
+      <c r="A6" s="53"/>
       <c r="B6" s="8" t="s">
         <v>54</v>
       </c>
@@ -1297,7 +1297,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="46.5" customHeight="1">
-      <c r="A7" s="17"/>
+      <c r="A7" s="54"/>
       <c r="B7" s="11" t="s">
         <v>55</v>
       </c>
@@ -1319,7 +1319,7 @@
     </row>
     <row r="8" spans="1:7" ht="15.75" thickBot="1"/>
     <row r="9" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="52" t="s">
         <v>10</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -1342,28 +1342,28 @@
       </c>
     </row>
     <row r="10" spans="1:7" ht="57" customHeight="1" thickBot="1">
-      <c r="A10" s="16"/>
+      <c r="A10" s="53"/>
       <c r="B10" s="8" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>61</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>63</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="G10" s="18" t="s">
+      <c r="G10" s="55" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="56.25" customHeight="1">
-      <c r="A11" s="17"/>
+      <c r="A11" s="54"/>
       <c r="B11" s="3" t="s">
         <v>57</v>
       </c>
@@ -1371,19 +1371,19 @@
         <v>6</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="G11" s="19"/>
+      <c r="G11" s="56"/>
     </row>
     <row r="12" spans="1:7" ht="15.75" thickBot="1"/>
     <row r="13" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="52" t="s">
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -1406,28 +1406,28 @@
       </c>
     </row>
     <row r="14" spans="1:7" ht="57" customHeight="1" thickBot="1">
-      <c r="A14" s="16"/>
+      <c r="A14" s="53"/>
       <c r="B14" s="8" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C14" s="14" t="s">
         <v>56</v>
       </c>
       <c r="D14" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>61</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>63</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="G14" s="18" t="s">
+      <c r="G14" s="55" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="56.25" customHeight="1">
-      <c r="A15" s="17"/>
+      <c r="A15" s="54"/>
       <c r="B15" s="3" t="s">
         <v>57</v>
       </c>
@@ -1435,19 +1435,19 @@
         <v>7</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="G15" s="19"/>
+      <c r="G15" s="56"/>
     </row>
     <row r="16" spans="1:7" ht="15.75" thickBot="1"/>
     <row r="17" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A17" s="15" t="s">
+      <c r="A17" s="57" t="s">
         <v>25</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -1470,28 +1470,28 @@
       </c>
     </row>
     <row r="18" spans="1:7" ht="57" customHeight="1" thickBot="1">
-      <c r="A18" s="16"/>
+      <c r="A18" s="53"/>
       <c r="B18" s="8" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>27</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="G18" s="18" t="s">
+      <c r="G18" s="55" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="56.25" customHeight="1">
-      <c r="A19" s="17"/>
+      <c r="A19" s="54"/>
       <c r="B19" s="3" t="s">
         <v>57</v>
       </c>
@@ -1499,100 +1499,100 @@
         <v>7</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F19" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="G19" s="19"/>
+      <c r="G19" s="56"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="B21" s="25" t="s">
+      <c r="B21" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C21" s="25" t="s">
+      <c r="C21" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="D21" s="25" t="s">
+      <c r="D21" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="E21" s="25" t="s">
+      <c r="E21" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="F21" s="26" t="s">
+      <c r="F21" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="G21" s="27"/>
+      <c r="G21" s="47"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="B22" s="28">
+      <c r="B22" s="16">
         <v>1</v>
       </c>
-      <c r="C22" s="28" t="s">
+      <c r="C22" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="D22" s="29">
+      <c r="D22" s="17">
         <v>1000</v>
       </c>
-      <c r="E22" s="29"/>
-      <c r="F22" s="30" t="s">
+      <c r="E22" s="17"/>
+      <c r="F22" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="G22" s="31"/>
+      <c r="G22" s="29"/>
     </row>
     <row r="23" spans="1:7" ht="25.5">
-      <c r="B23" s="28">
+      <c r="B23" s="16">
         <v>2</v>
       </c>
-      <c r="C23" s="28" t="s">
+      <c r="C23" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="D23" s="32">
+      <c r="D23" s="18">
         <v>1000</v>
       </c>
-      <c r="E23" s="33"/>
-      <c r="F23" s="30" t="s">
+      <c r="E23" s="19"/>
+      <c r="F23" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="G23" s="31"/>
+      <c r="G23" s="29"/>
     </row>
     <row r="24" spans="1:7" ht="51">
-      <c r="B24" s="28">
+      <c r="B24" s="16">
         <v>3</v>
       </c>
-      <c r="C24" s="34" t="s">
+      <c r="C24" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="D24" s="32">
+      <c r="D24" s="18">
         <v>100</v>
       </c>
-      <c r="E24" s="43"/>
-      <c r="F24" s="35" t="s">
+      <c r="E24" s="23"/>
+      <c r="F24" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="G24" s="36"/>
+      <c r="G24" s="22"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="B25" s="37" t="s">
+      <c r="B25" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="C25" s="38"/>
-      <c r="D25" s="39">
+      <c r="C25" s="39"/>
+      <c r="D25" s="40">
         <f>D22*D23 + D22*D24</f>
         <v>1100000</v>
       </c>
-      <c r="E25" s="40"/>
-      <c r="F25" s="41"/>
-      <c r="G25" s="42"/>
+      <c r="E25" s="41"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="43"/>
     </row>
     <row r="26" spans="1:7" ht="38.25">
-      <c r="B26" s="28">
+      <c r="B26" s="16">
         <v>1</v>
       </c>
-      <c r="C26" s="28" t="s">
+      <c r="C26" s="16" t="s">
         <v>40</v>
       </c>
       <c r="D26" s="44">
@@ -1600,117 +1600,103 @@
         <v>0.30000000000000004</v>
       </c>
       <c r="E26" s="45"/>
-      <c r="F26" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="G26" s="31"/>
+      <c r="F26" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="G26" s="29"/>
     </row>
     <row r="27" spans="1:7" ht="25.5">
-      <c r="B27" s="28">
+      <c r="B27" s="16">
         <v>3</v>
       </c>
-      <c r="C27" s="28" t="s">
+      <c r="C27" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="D27" s="46">
+      <c r="D27" s="36">
         <f>D25/1000000</f>
         <v>1.1000000000000001</v>
       </c>
-      <c r="E27" s="47"/>
-      <c r="F27" s="30" t="s">
+      <c r="E27" s="37"/>
+      <c r="F27" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="G27" s="31"/>
+      <c r="G27" s="29"/>
     </row>
     <row r="28" spans="1:7" ht="25.5">
-      <c r="B28" s="28">
+      <c r="B28" s="16">
         <v>4</v>
       </c>
-      <c r="C28" s="28" t="s">
+      <c r="C28" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="D28" s="46">
+      <c r="D28" s="36">
         <f>(D22*D23*0.2)/1000000</f>
         <v>0.2</v>
       </c>
-      <c r="E28" s="47"/>
-      <c r="F28" s="30" t="s">
+      <c r="E28" s="37"/>
+      <c r="F28" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="G28" s="31"/>
+      <c r="G28" s="29"/>
     </row>
     <row r="29" spans="1:7" ht="25.5">
-      <c r="B29" s="28">
+      <c r="B29" s="16">
         <v>5</v>
       </c>
-      <c r="C29" s="28" t="s">
+      <c r="C29" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="D29" s="48">
+      <c r="D29" s="24">
         <v>10</v>
       </c>
-      <c r="E29" s="49">
+      <c r="E29" s="25">
         <f>SUM(D26:E28)/(1 - D29/100)</f>
         <v>1.7777777777777779</v>
       </c>
-      <c r="F29" s="30" t="s">
+      <c r="F29" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="G29" s="31"/>
+      <c r="G29" s="29"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="B30" s="50" t="s">
+      <c r="B30" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="C30" s="51"/>
-      <c r="D30" s="52">
+      <c r="C30" s="31"/>
+      <c r="D30" s="32">
         <f>E29</f>
         <v>1.7777777777777779</v>
       </c>
-      <c r="E30" s="53"/>
-      <c r="F30" s="54"/>
-      <c r="G30" s="55"/>
+      <c r="E30" s="33"/>
+      <c r="F30" s="34"/>
+      <c r="G30" s="35"/>
     </row>
     <row r="32" spans="1:7" ht="30">
-      <c r="B32" s="56" t="s">
+      <c r="B32" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="C32" s="57" t="s">
+      <c r="C32" s="27" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="33" spans="2:3" ht="90">
-      <c r="B33" s="56" t="s">
+      <c r="B33" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="C33" s="57" t="s">
+      <c r="C33" s="27" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="34" spans="2:3" ht="90">
-      <c r="B34" s="56" t="s">
+      <c r="B34" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="C34" s="57" t="s">
+      <c r="C34" s="27" t="s">
         <v>44</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:G26"/>
     <mergeCell ref="F21:G21"/>
     <mergeCell ref="F22:G22"/>
     <mergeCell ref="A3:F3"/>
@@ -1723,6 +1709,20 @@
     <mergeCell ref="A13:A15"/>
     <mergeCell ref="G14:G15"/>
     <mergeCell ref="A5:A7"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:G28"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/tech/JMocha_시스템_사이징_사용자수별.xlsx
+++ b/docs/tech/JMocha_시스템_사이징_사용자수별.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="65">
   <si>
     <t>Software</t>
   </si>
@@ -322,28 +322,7 @@
     <t>MariaDB</t>
   </si>
   <si>
-    <t>1 x 4core
-2.4GHz</t>
-  </si>
-  <si>
-    <t>1 x 8core
-2.4GHz</t>
-  </si>
-  <si>
-    <t>1 x 16core
-2.4GHz</t>
-  </si>
-  <si>
-    <t>36GB</t>
-  </si>
-  <si>
-    <t>12GB</t>
-  </si>
-  <si>
     <t>24GB</t>
-  </si>
-  <si>
-    <t>72GB</t>
   </si>
   <si>
     <t>메일 큐(1인당 100MB)및 LOG 사용량(1인당 200MB) (이중화시 서버간 공유되지 않음)</t>
@@ -367,6 +346,17 @@
   <si>
     <t>Tomcat,
 JMocha Mail Server</t>
+  </si>
+  <si>
+    <t>1 x 6core
+2.4GHz</t>
+  </si>
+  <si>
+    <t>48GB</t>
+  </si>
+  <si>
+    <t>1 x 12core
+2.4GHz</t>
   </si>
 </sst>
 </file>
@@ -827,10 +817,70 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="14" fillId="6" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="14" fillId="6" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -855,66 +905,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="13" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="14" fillId="6" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="14" fillId="6" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1211,49 +1201,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="50"/>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
+      <c r="A2" s="34"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
     </row>
     <row r="3" spans="1:7" ht="30.75" customHeight="1">
-      <c r="A3" s="48" t="s">
+      <c r="A3" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
       <c r="G3" s="5"/>
     </row>
     <row r="4" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A4" s="51" t="s">
+      <c r="A4" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="51"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
+      <c r="B4" s="35"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
     </row>
     <row r="5" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="36" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -1276,7 +1266,7 @@
       </c>
     </row>
     <row r="6" spans="1:7" ht="74.25" customHeight="1" thickBot="1">
-      <c r="A6" s="53"/>
+      <c r="A6" s="37"/>
       <c r="B6" s="8" t="s">
         <v>54</v>
       </c>
@@ -1297,7 +1287,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="46.5" customHeight="1">
-      <c r="A7" s="54"/>
+      <c r="A7" s="38"/>
       <c r="B7" s="11" t="s">
         <v>55</v>
       </c>
@@ -1319,7 +1309,7 @@
     </row>
     <row r="8" spans="1:7" ht="15.75" thickBot="1"/>
     <row r="9" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="36" t="s">
         <v>10</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -1342,28 +1332,28 @@
       </c>
     </row>
     <row r="10" spans="1:7" ht="57" customHeight="1" thickBot="1">
-      <c r="A10" s="53"/>
+      <c r="A10" s="37"/>
       <c r="B10" s="8" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="G10" s="55" t="s">
+      <c r="G10" s="39" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="56.25" customHeight="1">
-      <c r="A11" s="54"/>
+      <c r="A11" s="38"/>
       <c r="B11" s="3" t="s">
         <v>57</v>
       </c>
@@ -1371,19 +1361,19 @@
         <v>6</v>
       </c>
       <c r="D11" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>58</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>62</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="G11" s="56"/>
+      <c r="G11" s="40"/>
     </row>
     <row r="12" spans="1:7" ht="15.75" thickBot="1"/>
     <row r="13" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A13" s="52" t="s">
+      <c r="A13" s="36" t="s">
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -1406,28 +1396,28 @@
       </c>
     </row>
     <row r="14" spans="1:7" ht="57" customHeight="1" thickBot="1">
-      <c r="A14" s="53"/>
+      <c r="A14" s="37"/>
       <c r="B14" s="8" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C14" s="14" t="s">
         <v>56</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="G14" s="55" t="s">
+      <c r="G14" s="39" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="56.25" customHeight="1">
-      <c r="A15" s="54"/>
+      <c r="A15" s="38"/>
       <c r="B15" s="3" t="s">
         <v>57</v>
       </c>
@@ -1435,19 +1425,19 @@
         <v>7</v>
       </c>
       <c r="D15" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>58</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>62</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="G15" s="56"/>
+      <c r="G15" s="40"/>
     </row>
     <row r="16" spans="1:7" ht="15.75" thickBot="1"/>
     <row r="17" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A17" s="57" t="s">
+      <c r="A17" s="41" t="s">
         <v>25</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -1470,28 +1460,28 @@
       </c>
     </row>
     <row r="18" spans="1:7" ht="57" customHeight="1" thickBot="1">
-      <c r="A18" s="53"/>
+      <c r="A18" s="37"/>
       <c r="B18" s="8" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>27</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="G18" s="55" t="s">
+      <c r="G18" s="39" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="56.25" customHeight="1">
-      <c r="A19" s="54"/>
+      <c r="A19" s="38"/>
       <c r="B19" s="3" t="s">
         <v>57</v>
       </c>
@@ -1499,7 +1489,7 @@
         <v>7</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E19" s="13" t="s">
         <v>63</v>
@@ -1507,7 +1497,7 @@
       <c r="F19" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="G19" s="56"/>
+      <c r="G19" s="40"/>
     </row>
     <row r="21" spans="1:7">
       <c r="B21" s="15" t="s">
@@ -1522,10 +1512,10 @@
       <c r="E21" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="F21" s="46" t="s">
+      <c r="F21" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="G21" s="47"/>
+      <c r="G21" s="29"/>
     </row>
     <row r="22" spans="1:7">
       <c r="B22" s="16">
@@ -1538,10 +1528,10 @@
         <v>1000</v>
       </c>
       <c r="E22" s="17"/>
-      <c r="F22" s="28" t="s">
+      <c r="F22" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="G22" s="29"/>
+      <c r="G22" s="31"/>
     </row>
     <row r="23" spans="1:7" ht="25.5">
       <c r="B23" s="16">
@@ -1554,10 +1544,10 @@
         <v>1000</v>
       </c>
       <c r="E23" s="19"/>
-      <c r="F23" s="28" t="s">
+      <c r="F23" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="G23" s="29"/>
+      <c r="G23" s="31"/>
     </row>
     <row r="24" spans="1:7" ht="51">
       <c r="B24" s="16">
@@ -1576,17 +1566,17 @@
       <c r="G24" s="22"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="B25" s="38" t="s">
+      <c r="B25" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="C25" s="39"/>
-      <c r="D25" s="40">
+      <c r="C25" s="43"/>
+      <c r="D25" s="44">
         <f>D22*D23 + D22*D24</f>
         <v>1100000</v>
       </c>
-      <c r="E25" s="41"/>
-      <c r="F25" s="42"/>
-      <c r="G25" s="43"/>
+      <c r="E25" s="45"/>
+      <c r="F25" s="46"/>
+      <c r="G25" s="47"/>
     </row>
     <row r="26" spans="1:7" ht="38.25">
       <c r="B26" s="16">
@@ -1595,15 +1585,15 @@
       <c r="C26" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="D26" s="44">
+      <c r="D26" s="48">
         <f>0.0001*D22 + 0.0002*D22</f>
         <v>0.30000000000000004</v>
       </c>
-      <c r="E26" s="45"/>
-      <c r="F26" s="28" t="s">
-        <v>65</v>
-      </c>
-      <c r="G26" s="29"/>
+      <c r="E26" s="49"/>
+      <c r="F26" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="G26" s="31"/>
     </row>
     <row r="27" spans="1:7" ht="25.5">
       <c r="B27" s="16">
@@ -1612,15 +1602,15 @@
       <c r="C27" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="D27" s="36">
+      <c r="D27" s="56">
         <f>D25/1000000</f>
         <v>1.1000000000000001</v>
       </c>
-      <c r="E27" s="37"/>
-      <c r="F27" s="28" t="s">
+      <c r="E27" s="57"/>
+      <c r="F27" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="G27" s="29"/>
+      <c r="G27" s="31"/>
     </row>
     <row r="28" spans="1:7" ht="25.5">
       <c r="B28" s="16">
@@ -1629,15 +1619,15 @@
       <c r="C28" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="D28" s="36">
+      <c r="D28" s="56">
         <f>(D22*D23*0.2)/1000000</f>
         <v>0.2</v>
       </c>
-      <c r="E28" s="37"/>
-      <c r="F28" s="28" t="s">
+      <c r="E28" s="57"/>
+      <c r="F28" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="G28" s="29"/>
+      <c r="G28" s="31"/>
     </row>
     <row r="29" spans="1:7" ht="25.5">
       <c r="B29" s="16">
@@ -1653,23 +1643,23 @@
         <f>SUM(D26:E28)/(1 - D29/100)</f>
         <v>1.7777777777777779</v>
       </c>
-      <c r="F29" s="28" t="s">
+      <c r="F29" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="G29" s="29"/>
+      <c r="G29" s="31"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="B30" s="30" t="s">
+      <c r="B30" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="C30" s="31"/>
-      <c r="D30" s="32">
+      <c r="C30" s="51"/>
+      <c r="D30" s="52">
         <f>E29</f>
         <v>1.7777777777777779</v>
       </c>
-      <c r="E30" s="33"/>
-      <c r="F30" s="34"/>
-      <c r="G30" s="35"/>
+      <c r="E30" s="53"/>
+      <c r="F30" s="54"/>
+      <c r="G30" s="55"/>
     </row>
     <row r="32" spans="1:7" ht="30">
       <c r="B32" s="26" t="s">
@@ -1697,6 +1687,20 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:G26"/>
     <mergeCell ref="F21:G21"/>
     <mergeCell ref="F22:G22"/>
     <mergeCell ref="A3:F3"/>
@@ -1709,20 +1713,6 @@
     <mergeCell ref="A13:A15"/>
     <mergeCell ref="G14:G15"/>
     <mergeCell ref="A5:A7"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:G28"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
